--- a/cert-data/Healthcare-Certification-Report-08.31.2026.xlsx
+++ b/cert-data/Healthcare-Certification-Report-08.31.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/Dashboard Reports/Healthcare Dashboard Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{949EFF26-E5C7-4614-978C-5FF20646DA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66BE3CA-3402-495F-A94E-D987FDA97556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Certification Report" sheetId="1" r:id="rId1"/>
@@ -356,6 +356,15 @@
     <t>NDemeduk@kmbs.konicaminolta.us</t>
   </si>
   <si>
+    <t>Leigh</t>
+  </si>
+  <si>
+    <t>Whitaker</t>
+  </si>
+  <si>
+    <t>TWhitaker@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
     <t>Andrea</t>
   </si>
   <si>
@@ -828,15 +837,6 @@
   </si>
   <si>
     <t>TWatling@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Leigh</t>
-  </si>
-  <si>
-    <t>Whitaker</t>
-  </si>
-  <si>
-    <t>TWhitaker@kmbs.konicaminolta.us</t>
   </si>
   <si>
     <t>Philip</t>
@@ -870,7 +870,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1041,16 +1041,6 @@
       <color rgb="FF9C0006"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1409,7 +1399,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1440,13 +1430,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1810,7 +1793,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}" name="Table1" displayName="Table1" ref="A1:T67" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:T67" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T67">
     <sortCondition descending="1" ref="T1:T67"/>
   </sortState>
@@ -2176,7 +2158,7 @@
     <col min="12" max="12" width="36.42578125" style="2" customWidth="1"/>
     <col min="13" max="13" width="34.85546875" style="2" customWidth="1"/>
     <col min="14" max="14" width="18.28515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.85546875" style="2" customWidth="1"/>
     <col min="17" max="17" width="37.140625" style="2" customWidth="1"/>
     <col min="18" max="18" width="44" style="4" bestFit="1" customWidth="1"/>
@@ -3275,7 +3257,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="2">
-        <v>105722</v>
+        <v>122812</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>20</v>
@@ -3290,7 +3272,7 @@
         <v>108</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
@@ -3317,7 +3299,7 @@
         <v>31</v>
       </c>
       <c r="O18" s="8">
-        <v>34169</v>
+        <v>43557</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>32</v>
@@ -3325,115 +3307,121 @@
       <c r="Q18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R18" s="1"/>
-      <c r="T18" s="11" t="s">
-        <v>110</v>
+      <c r="R18" s="9">
+        <v>46265</v>
+      </c>
+      <c r="S18" s="1" t="str">
+        <f>"FY"&amp;YEAR(R18)-IF(MONTH(R18)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R18),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T18" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="2">
-        <v>129377</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>105722</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" s="8">
+        <v>34169</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="T19" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O19" s="8">
-        <v>46132</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="9"/>
-      <c r="T19" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="2">
-        <v>129570</v>
+        <v>129377</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="N20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O20" s="8">
-        <v>46209</v>
+        <v>46132</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>32</v>
@@ -3441,30 +3429,36 @@
       <c r="Q20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R20" s="9"/>
-      <c r="T20" s="11" t="s">
-        <v>110</v>
+      <c r="R20" s="9">
+        <v>46265</v>
+      </c>
+      <c r="S20" s="1" t="str">
+        <f>"FY"&amp;YEAR(R20)-IF(MONTH(R20)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R20),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="2">
-        <v>126128</v>
-      </c>
-      <c r="B21" s="7" t="s">
+        <v>129570</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>25</v>
@@ -3476,22 +3470,22 @@
         <v>26</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O21" s="8">
-        <v>44907</v>
+        <v>46209</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>32</v>
@@ -3501,55 +3495,55 @@
       </c>
       <c r="R21" s="9"/>
       <c r="T21" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="2">
-        <v>106003</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>126128</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="M22" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O22" s="8">
-        <v>37967</v>
+        <v>44907</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>32</v>
@@ -3559,15 +3553,15 @@
       </c>
       <c r="R22" s="9"/>
       <c r="T22" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="2">
-        <v>115144</v>
-      </c>
-      <c r="B23" s="7" t="s">
+        <v>106003</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3580,34 +3574,34 @@
         <v>137</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O23" s="8">
-        <v>41362</v>
+        <v>37967</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>32</v>
@@ -3617,19 +3611,19 @@
       </c>
       <c r="R23" s="9"/>
       <c r="T23" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U23" s="2"/>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="2">
-        <v>128348</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>115144</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>139</v>
@@ -3644,28 +3638,28 @@
         <v>25</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O24" s="8">
-        <v>45642</v>
+        <v>41362</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>32</v>
@@ -3675,55 +3669,55 @@
       </c>
       <c r="R24" s="9"/>
       <c r="T24" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="2">
-        <v>128013</v>
-      </c>
-      <c r="B25" s="7" t="s">
+        <v>128348</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="M25" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O25" s="8">
-        <v>45544</v>
+        <v>45642</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>32</v>
@@ -3733,55 +3727,55 @@
       </c>
       <c r="R25" s="9"/>
       <c r="T25" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="2">
-        <v>111249</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>128013</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O26" s="8">
-        <v>40336</v>
+        <v>45544</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>32</v>
@@ -3791,55 +3785,55 @@
       </c>
       <c r="R26" s="9"/>
       <c r="T26" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="2">
-        <v>123471</v>
-      </c>
-      <c r="B27" s="7" t="s">
+        <v>111249</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="L27" s="2" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O27" s="8">
-        <v>43753</v>
+        <v>40336</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>32</v>
@@ -3849,55 +3843,55 @@
       </c>
       <c r="R27" s="9"/>
       <c r="T27" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="2">
-        <v>129427</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>123471</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="N28" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O28" s="8">
-        <v>46146</v>
+        <v>43753</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>32</v>
@@ -3907,55 +3901,55 @@
       </c>
       <c r="R28" s="9"/>
       <c r="T28" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U28" s="2"/>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="2">
-        <v>127473</v>
+        <v>129427</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="M29" s="2" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O29" s="8">
-        <v>45393</v>
+        <v>46146</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>32</v>
@@ -3965,15 +3959,15 @@
       </c>
       <c r="R29" s="9"/>
       <c r="T29" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U29" s="2"/>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="2">
-        <v>124636</v>
-      </c>
-      <c r="B30" s="7" t="s">
+        <v>127473</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -3986,34 +3980,34 @@
         <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O30" s="8">
-        <v>44396</v>
+        <v>45393</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>32</v>
@@ -4023,28 +4017,28 @@
       </c>
       <c r="R30" s="9"/>
       <c r="T30" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="2">
-        <v>120999</v>
-      </c>
-      <c r="B31" s="3" t="s">
+        <v>124636</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>25</v>
@@ -4056,22 +4050,22 @@
         <v>26</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O31" s="8">
-        <v>44403</v>
+        <v>44396</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>32</v>
@@ -4081,15 +4075,15 @@
       </c>
       <c r="R31" s="9"/>
       <c r="T31" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U31" s="2"/>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="2">
-        <v>128321</v>
-      </c>
-      <c r="B32" s="7" t="s">
+        <v>120999</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -4102,34 +4096,34 @@
         <v>169</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O32" s="8">
-        <v>45664</v>
+        <v>44403</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>32</v>
@@ -4139,13 +4133,13 @@
       </c>
       <c r="R32" s="9"/>
       <c r="T32" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="2">
-        <v>129309</v>
+        <v>128321</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>20</v>
@@ -4160,34 +4154,34 @@
         <v>172</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O33" s="8">
-        <v>46113</v>
+        <v>45664</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>32</v>
@@ -4197,15 +4191,15 @@
       </c>
       <c r="R33" s="9"/>
       <c r="T33" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U33" s="2"/>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="2">
-        <v>129105</v>
-      </c>
-      <c r="B34" s="3" t="s">
+        <v>129309</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -4218,7 +4212,7 @@
         <v>175</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>25</v>
@@ -4230,22 +4224,22 @@
         <v>26</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O34" s="8">
-        <v>45985</v>
+        <v>46113</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>32</v>
@@ -4255,15 +4249,15 @@
       </c>
       <c r="R34" s="9"/>
       <c r="T34" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U34" s="2"/>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" s="2">
-        <v>106138</v>
-      </c>
-      <c r="B35" s="7" t="s">
+        <v>129105</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -4276,34 +4270,34 @@
         <v>178</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O35" s="8">
-        <v>35492</v>
+        <v>45985</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>32</v>
@@ -4313,13 +4307,13 @@
       </c>
       <c r="R35" s="9"/>
       <c r="T35" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U35" s="2"/>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="2">
-        <v>115424</v>
+        <v>106138</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>20</v>
@@ -4334,34 +4328,34 @@
         <v>181</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O36" s="8">
-        <v>41456</v>
+        <v>35492</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>32</v>
@@ -4371,15 +4365,15 @@
       </c>
       <c r="R36" s="9"/>
       <c r="T36" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U36" s="2"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="2">
-        <v>125940</v>
-      </c>
-      <c r="B37" s="3" t="s">
+        <v>115424</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -4392,34 +4386,34 @@
         <v>184</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O37" s="8">
-        <v>44825</v>
+        <v>41456</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>32</v>
@@ -4429,15 +4423,15 @@
       </c>
       <c r="R37" s="9"/>
       <c r="T37" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U37" s="2"/>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="2">
-        <v>120343</v>
-      </c>
-      <c r="B38" s="7" t="s">
+        <v>125940</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -4450,34 +4444,34 @@
         <v>187</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O38" s="8">
-        <v>42821</v>
+        <v>44825</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>32</v>
@@ -4487,45 +4481,45 @@
       </c>
       <c r="R38" s="9"/>
       <c r="T38" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="2">
-        <v>103885</v>
-      </c>
-      <c r="B39" s="3" t="s">
+        <v>120343</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>30</v>
@@ -4534,7 +4528,7 @@
         <v>31</v>
       </c>
       <c r="O39" s="8">
-        <v>45950</v>
+        <v>42821</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>32</v>
@@ -4544,27 +4538,27 @@
       </c>
       <c r="R39" s="9"/>
       <c r="T39" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="2">
-        <v>127835</v>
+        <v>103885</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>25</v>
@@ -4576,22 +4570,22 @@
         <v>26</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O40" s="8">
-        <v>45488</v>
+        <v>45950</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>32</v>
@@ -4601,12 +4595,12 @@
       </c>
       <c r="R40" s="9"/>
       <c r="T40" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="2">
-        <v>102475</v>
+        <v>127835</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>20</v>
@@ -4621,7 +4615,7 @@
         <v>193</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>25</v>
@@ -4633,22 +4627,22 @@
         <v>26</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O41" s="14">
-        <v>39580</v>
+      <c r="O41" s="8">
+        <v>45488</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>32</v>
@@ -4658,14 +4652,14 @@
       </c>
       <c r="R41" s="9"/>
       <c r="T41" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="2">
-        <v>126595</v>
-      </c>
-      <c r="B42" s="7" t="s">
+        <v>102475</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -4678,7 +4672,7 @@
         <v>196</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>25</v>
@@ -4690,22 +4684,22 @@
         <v>26</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O42" s="8">
-        <v>45069</v>
+        <v>39580</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>32</v>
@@ -4715,12 +4709,12 @@
       </c>
       <c r="R42" s="9"/>
       <c r="T42" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="2">
-        <v>128757</v>
+        <v>126595</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>20</v>
@@ -4735,34 +4729,34 @@
         <v>199</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O43" s="8">
-        <v>45796</v>
+        <v>45069</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>32</v>
@@ -4772,14 +4766,14 @@
       </c>
       <c r="R43" s="9"/>
       <c r="T43" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="2">
-        <v>128941</v>
-      </c>
-      <c r="B44" s="3" t="s">
+        <v>128757</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -4792,34 +4786,34 @@
         <v>202</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O44" s="8">
-        <v>45902</v>
+        <v>45796</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>32</v>
@@ -4829,27 +4823,27 @@
       </c>
       <c r="R44" s="9"/>
       <c r="T44" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="2">
-        <v>129148</v>
-      </c>
-      <c r="B45" s="7" t="s">
+        <v>128941</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>25</v>
@@ -4861,13 +4855,13 @@
         <v>26</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>24</v>
@@ -4876,7 +4870,7 @@
         <v>31</v>
       </c>
       <c r="O45" s="8">
-        <v>45999</v>
+        <v>45902</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>32</v>
@@ -4886,27 +4880,27 @@
       </c>
       <c r="R45" s="9"/>
       <c r="T45" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="2">
-        <v>125769</v>
-      </c>
-      <c r="B46" s="3" t="s">
+        <v>129148</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>25</v>
@@ -4918,22 +4912,22 @@
         <v>26</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O46" s="8">
-        <v>44753</v>
+        <v>45999</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>32</v>
@@ -4943,18 +4937,18 @@
       </c>
       <c r="R46" s="9"/>
       <c r="T46" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="2">
-        <v>128291</v>
-      </c>
-      <c r="B47" s="7" t="s">
+        <v>125769</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>216</v>
@@ -4963,34 +4957,34 @@
         <v>217</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O47" s="8">
-        <v>45628</v>
+        <v>44753</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>32</v>
@@ -5000,12 +4994,12 @@
       </c>
       <c r="R47" s="9"/>
       <c r="T47" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48" s="2">
-        <v>126110</v>
+        <v>128291</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>20</v>
@@ -5020,25 +5014,25 @@
         <v>220</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>24</v>
@@ -5047,7 +5041,7 @@
         <v>31</v>
       </c>
       <c r="O48" s="8">
-        <v>44900</v>
+        <v>45628</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>32</v>
@@ -5057,14 +5051,14 @@
       </c>
       <c r="R48" s="9"/>
       <c r="T48" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" s="2">
-        <v>103900</v>
-      </c>
-      <c r="B49" s="3" t="s">
+        <v>126110</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -5077,7 +5071,7 @@
         <v>223</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>224</v>
+        <v>51</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>25</v>
@@ -5089,13 +5083,13 @@
         <v>26</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>24</v>
@@ -5104,7 +5098,7 @@
         <v>31</v>
       </c>
       <c r="O49" s="8">
-        <v>39601</v>
+        <v>44900</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>32</v>
@@ -5114,18 +5108,18 @@
       </c>
       <c r="R49" s="9"/>
       <c r="T49" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:20">
       <c r="A50" s="2">
-        <v>117563</v>
-      </c>
-      <c r="B50" s="7" t="s">
+        <v>103900</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>225</v>
@@ -5134,25 +5128,25 @@
         <v>226</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>51</v>
+        <v>227</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>24</v>
@@ -5161,7 +5155,7 @@
         <v>31</v>
       </c>
       <c r="O50" s="8">
-        <v>42100</v>
+        <v>39601</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>32</v>
@@ -5171,18 +5165,18 @@
       </c>
       <c r="R50" s="9"/>
       <c r="T50" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" s="2">
-        <v>104738</v>
+        <v>117563</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>228</v>
@@ -5191,34 +5185,34 @@
         <v>229</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O51" s="8">
-        <v>39335</v>
+        <v>42100</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>32</v>
@@ -5228,54 +5222,54 @@
       </c>
       <c r="R51" s="9"/>
       <c r="T51" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" s="2">
-        <v>103915</v>
+        <v>104738</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>39</v>
+        <v>231</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O52" s="8">
-        <v>36130</v>
+        <v>39335</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>32</v>
@@ -5285,54 +5279,54 @@
       </c>
       <c r="R52" s="9"/>
       <c r="T52" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="2">
-        <v>123862</v>
-      </c>
-      <c r="B53" s="3" t="s">
+        <v>103915</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="L53" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="M53" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O53" s="8">
-        <v>45706</v>
+        <v>36130</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>32</v>
@@ -5342,14 +5336,14 @@
       </c>
       <c r="R53" s="9"/>
       <c r="T53" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" s="2">
-        <v>127826</v>
-      </c>
-      <c r="B54" s="7" t="s">
+        <v>123862</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -5362,34 +5356,34 @@
         <v>238</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O54" s="8">
-        <v>45481</v>
+        <v>45706</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>32</v>
@@ -5399,14 +5393,14 @@
       </c>
       <c r="R54" s="9"/>
       <c r="T54" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="2">
-        <v>127239</v>
-      </c>
-      <c r="B55" s="3" t="s">
+        <v>127826</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -5419,25 +5413,25 @@
         <v>241</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>56</v>
@@ -5446,7 +5440,7 @@
         <v>31</v>
       </c>
       <c r="O55" s="8">
-        <v>45278</v>
+        <v>45481</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>32</v>
@@ -5455,56 +5449,55 @@
         <v>33</v>
       </c>
       <c r="R55" s="9"/>
-      <c r="S55" s="1"/>
       <c r="T55" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="2">
-        <v>127857</v>
-      </c>
-      <c r="B56" s="2" t="s">
+        <v>127239</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>244</v>
+        <v>75</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O56" s="8">
-        <v>45495</v>
+        <v>45278</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>32</v>
@@ -5513,47 +5506,47 @@
         <v>33</v>
       </c>
       <c r="R56" s="9"/>
-      <c r="S56" s="2"/>
+      <c r="S56" s="1"/>
       <c r="T56" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="2">
-        <v>126783</v>
-      </c>
-      <c r="B57" s="7" t="s">
+        <v>127857</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>30</v>
@@ -5562,7 +5555,7 @@
         <v>31</v>
       </c>
       <c r="O57" s="8">
-        <v>45117</v>
+        <v>45495</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>32</v>
@@ -5571,15 +5564,16 @@
         <v>33</v>
       </c>
       <c r="R57" s="9"/>
+      <c r="S57" s="2"/>
       <c r="T57" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" s="2">
-        <v>129153</v>
-      </c>
-      <c r="B58" s="3" t="s">
+        <v>126783</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -5592,34 +5586,34 @@
         <v>250</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O58" s="8">
-        <v>46006</v>
+        <v>45117</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>32</v>
@@ -5629,12 +5623,12 @@
       </c>
       <c r="R58" s="9"/>
       <c r="T58" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" s="2">
-        <v>128655</v>
+        <v>129153</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>20</v>
@@ -5649,34 +5643,34 @@
         <v>253</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O59" s="8">
-        <v>45761</v>
+        <v>46006</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>32</v>
@@ -5686,12 +5680,12 @@
       </c>
       <c r="R59" s="9"/>
       <c r="T59" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="2">
-        <v>128748</v>
+        <v>128655</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
@@ -5706,7 +5700,7 @@
         <v>256</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>25</v>
@@ -5718,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>24</v>
@@ -5733,7 +5727,7 @@
         <v>31</v>
       </c>
       <c r="O60" s="8">
-        <v>45811</v>
+        <v>45761</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>32</v>
@@ -5743,54 +5737,54 @@
       </c>
       <c r="R60" s="9"/>
       <c r="T60" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="2">
-        <v>128192</v>
-      </c>
-      <c r="B61" s="7" t="s">
+        <v>128748</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>115</v>
+        <v>257</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O61" s="8">
-        <v>45607</v>
+        <v>45811</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>32</v>
@@ -5800,24 +5794,24 @@
       </c>
       <c r="R61" s="9"/>
       <c r="T61" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" s="2">
-        <v>118369</v>
-      </c>
-      <c r="B62" s="3" t="s">
+        <v>128192</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>141</v>
@@ -5826,28 +5820,28 @@
         <v>25</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O62" s="8">
-        <v>42282</v>
+        <v>45607</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>32</v>
@@ -5857,27 +5851,27 @@
       </c>
       <c r="R62" s="9"/>
       <c r="T62" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" s="2">
-        <v>118764</v>
-      </c>
-      <c r="B63" s="7" t="s">
+        <v>118369</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>25</v>
@@ -5889,22 +5883,22 @@
         <v>26</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>243</v>
+        <v>22</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O63" s="8">
-        <v>42317</v>
+        <v>42282</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>32</v>
@@ -5914,45 +5908,45 @@
       </c>
       <c r="R63" s="9"/>
       <c r="T63" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" s="2">
-        <v>125310</v>
+        <v>118764</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>261</v>
+        <v>164</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>262</v>
+        <v>165</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>263</v>
+        <v>166</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>38</v>
+        <v>245</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>30</v>
@@ -5961,7 +5955,7 @@
         <v>31</v>
       </c>
       <c r="O64" s="8">
-        <v>44627</v>
+        <v>42317</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>32</v>
@@ -5971,12 +5965,12 @@
       </c>
       <c r="R64" s="9"/>
       <c r="T64" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" s="2">
-        <v>122812</v>
+        <v>125310</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>20</v>
@@ -5997,28 +5991,28 @@
         <v>25</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="O65" s="8">
-        <v>43557</v>
+        <v>44627</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>32</v>
@@ -6026,15 +6020,9 @@
       <c r="Q65" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R65" s="9">
-        <v>46265</v>
-      </c>
-      <c r="S65" s="13" t="str">
-        <f>"FY"&amp;YEAR(R65)-IF(MONTH(R65)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R65),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T65" s="12" t="s">
-        <v>20</v>
+      <c r="R65" s="9"/>
+      <c r="T65" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -6054,7 +6042,7 @@
         <v>269</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>25</v>
@@ -6091,7 +6079,7 @@
       </c>
       <c r="R66" s="9"/>
       <c r="T66" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -6111,7 +6099,7 @@
         <v>275</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>25</v>
@@ -6149,7 +6137,7 @@
       <c r="R67" s="9"/>
       <c r="S67" s="1"/>
       <c r="T67" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:20">
